--- a/converted_files/835/835-all-fields.xlsx
+++ b/converted_files/835/835-all-fields.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69e82c67836d7d05c9a02b3f</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69e82c67836d7d05c9a02b3f</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2073,7 +2073,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69e82c67836d7d05c9a02b3f</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2337,7 +2337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69e82c67836d7d05c9a02b3f</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2601,7 +2601,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69e82c67836d7d05c9a02b3f</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2849,7 +2849,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69e82c67836d7d05c9a02b3f</t>
         </is>
       </c>
       <c r="B7"/>
@@ -3143,7 +3143,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69e82c67836d7d05c9a02b3f</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/835/835-all-fields.xlsx
+++ b/converted_files/835/835-all-fields.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69efef04ad4799caa7f5b98c</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69efef04ad4799caa7f5b98c</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2073,7 +2073,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69efef04ad4799caa7f5b98c</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2337,7 +2337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69efef04ad4799caa7f5b98c</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2601,7 +2601,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69efef04ad4799caa7f5b98c</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2849,7 +2849,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69efef04ad4799caa7f5b98c</t>
         </is>
       </c>
       <c r="B7"/>
@@ -3143,7 +3143,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69446374c1a6b3ab024f4f3b</t>
+          <t>69efef04ad4799caa7f5b98c</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/835/835-all-fields.xlsx
+++ b/converted_files/835/835-all-fields.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02b3f</t>
+          <t>6a04cbecb80b363c8541f9ff</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02b3f</t>
+          <t>6a04cbecb80b363c8541f9ff</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2073,7 +2073,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02b3f</t>
+          <t>6a04cbecb80b363c8541f9ff</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2337,7 +2337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02b3f</t>
+          <t>6a04cbecb80b363c8541f9ff</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2601,7 +2601,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02b3f</t>
+          <t>6a04cbecb80b363c8541f9ff</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2849,7 +2849,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02b3f</t>
+          <t>6a04cbecb80b363c8541f9ff</t>
         </is>
       </c>
       <c r="B7"/>
@@ -3143,7 +3143,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69e82c67836d7d05c9a02b3f</t>
+          <t>6a04cbecb80b363c8541f9ff</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/835/835-all-fields.xlsx
+++ b/converted_files/835/835-all-fields.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f9ff</t>
+          <t>6a04cc5a1ef26d534baf1687</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f9ff</t>
+          <t>6a04cc5a1ef26d534baf1687</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2073,7 +2073,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f9ff</t>
+          <t>6a04cc5a1ef26d534baf1687</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2337,7 +2337,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f9ff</t>
+          <t>6a04cc5a1ef26d534baf1687</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2601,7 +2601,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f9ff</t>
+          <t>6a04cc5a1ef26d534baf1687</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2849,7 +2849,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f9ff</t>
+          <t>6a04cc5a1ef26d534baf1687</t>
         </is>
       </c>
       <c r="B7"/>
@@ -3143,7 +3143,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f9ff</t>
+          <t>6a04cc5a1ef26d534baf1687</t>
         </is>
       </c>
       <c r="B8"/>

--- a/converted_files/835/835-all-fields.xlsx
+++ b/converted_files/835/835-all-fields.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf1687</t>
+          <t>6a32cb6297613a0e49906af3</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>226.0</v>
+        <v>384.0</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>132.0</v>
+        <v>238.0</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>10.0</v>
@@ -1185,25 +1185,25 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>2200008888</t>
+          <t>456</t>
         </is>
       </c>
       <c r="U2" s="4" t="n">
-        <v>45756.0</v>
+        <v>43555.0</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>882509401093167</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>106609999</t>
+          <t>1512345678</t>
         </is>
       </c>
       <c r="X2" s="4" t="n">
@@ -1490,16 +1490,8 @@
           <t>12345678</t>
         </is>
       </c>
-      <c r="CZ2" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="DA2" s="3" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
+      <c r="CZ2"/>
+      <c r="DA2"/>
       <c r="DB2" s="3" t="inlineStr">
         <is>
           <t>CMS_PLAN_ID</t>
@@ -1653,7 +1645,7 @@
       </c>
       <c r="EU2" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="EV2"/>
@@ -1809,7 +1801,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf1687</t>
+          <t>6a32cb6297613a0e49906af3</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2073,7 +2065,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf1687</t>
+          <t>6a32cb6297613a0e49906af3</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2337,7 +2329,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf1687</t>
+          <t>6a32cb6297613a0e49906af3</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2601,7 +2593,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf1687</t>
+          <t>6a32cb6297613a0e49906af3</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2769,7 +2761,7 @@
         <v>99.0</v>
       </c>
       <c r="ER6" s="1" t="n">
-        <v>59.0</v>
+        <v>99.0</v>
       </c>
       <c r="ES6" t="n">
         <v>1.0</v>
@@ -2849,7 +2841,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf1687</t>
+          <t>6a32cb6297613a0e49906af3</t>
         </is>
       </c>
       <c r="B7"/>
@@ -3017,7 +3009,7 @@
         <v>73.0</v>
       </c>
       <c r="ER7" s="1" t="n">
-        <v>49.0</v>
+        <v>-3.0</v>
       </c>
       <c r="ES7" t="n">
         <v>1.0</v>
@@ -3143,7 +3135,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf1687</t>
+          <t>6a32cb6297613a0e49906af3</t>
         </is>
       </c>
       <c r="B8"/>
@@ -3308,7 +3300,7 @@
         </is>
       </c>
       <c r="EQ8" s="1" t="n">
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="ER8" s="1" t="n">
         <v>59.0</v>

--- a/converted_files/835/835-all-fields.xlsx
+++ b/converted_files/835/835-all-fields.xlsx
@@ -6,7 +6,9 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Payments and Service Lines" r:id="rId3" sheetId="1"/>
+    <sheet name="Transactions" r:id="rId3" sheetId="1"/>
+    <sheet name="ProviderAdjustments" r:id="rId4" sheetId="2"/>
+    <sheet name="Service Lines" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -59,6 +61,773 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AX2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionControlNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TotalPaymentAmount</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CreditOrDebitFlagCode</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentMethodType</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ReceiverAccountNumber</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CheckOrEftTraceNumber</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>PayerEin</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ProductionDate</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentificationType</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentifier</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>PayerName</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressCity</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressStateCode</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressZipCode</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1Name</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2Name</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentificationType</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentifier</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeLastNameOrOrgName</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine2</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressCity</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressStateCode</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressZipCode</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodName</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd2aaa71f5c1ede91a3a</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>835-all-fields.dat</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>35681</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>132.0</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>43555.0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>1512345678</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>43538.0</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>DELTA DENTAL OF ABC</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
+      <c r="Q2"/>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>JANE DOE</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>9005555555</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="Z2"/>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>myplan.com/policies</t>
+        </is>
+      </c>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="inlineStr">
+        <is>
+          <t>HEALTH_INDUSTRY_NUMBER</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>EIN</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
+          <t>999994703</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="inlineStr">
+        <is>
+          <t>050595</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>BAN DDS LLC</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>225 MAIN STREET</t>
+        </is>
+      </c>
+      <c r="AN2"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>CENTERVILLE</t>
+        </is>
+      </c>
+      <c r="AP2" s="3" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr">
+        <is>
+          <t>17111</t>
+        </is>
+      </c>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0505</t>
+        </is>
+      </c>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>9618215141</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:BC1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionControlNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TotalPaymentAmount</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CreditOrDebitFlagCode</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentMethodType</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ReceiverAccountNumber</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CheckOrEftTraceNumber</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>PayerEin</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ProductionDate</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentificationType</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentifier</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>PayerName</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressCity</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressStateCode</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressZipCode</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1Name</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2Name</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentificationType</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentifier</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeLastNameOrOrgName</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine2</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressCity</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressStateCode</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressZipCode</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodName</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+        </is>
+      </c>
+      <c r="AY1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderIdentifier</t>
+        </is>
+      </c>
+      <c r="AZ1" s="3" t="inlineStr">
+        <is>
+          <t>FiscalPeriodDate</t>
+        </is>
+      </c>
+      <c r="BA1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentReason</t>
+        </is>
+      </c>
+      <c r="BB1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentReferenceIdentification</t>
+        </is>
+      </c>
+      <c r="BC1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentAmount</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:GZ8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -410,37 +1179,37 @@
       </c>
       <c r="BR1" s="3" t="inlineStr">
         <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="BS1" s="3" t="inlineStr">
+        <is>
           <t>PayeeLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="BS1" s="3" t="inlineStr">
+      <c r="BT1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressLine</t>
         </is>
       </c>
-      <c r="BT1" s="3" t="inlineStr">
+      <c r="BU1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressLine2</t>
         </is>
       </c>
-      <c r="BU1" s="3" t="inlineStr">
+      <c r="BV1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressCity</t>
         </is>
       </c>
-      <c r="BV1" s="3" t="inlineStr">
+      <c r="BW1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressStateCode</t>
         </is>
       </c>
-      <c r="BW1" s="3" t="inlineStr">
+      <c r="BX1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressZipCode</t>
-        </is>
-      </c>
-      <c r="BX1" s="3" t="inlineStr">
-        <is>
-          <t>PayeeContacts</t>
         </is>
       </c>
       <c r="BY1" s="3" t="inlineStr">
@@ -1107,7 +1876,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906af3</t>
+          <t>6a68fd2aaa71f5c1ede91a9b</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1370,31 +2139,35 @@
       </c>
       <c r="BR2" s="3" t="inlineStr">
         <is>
+          <t>050595</t>
+        </is>
+      </c>
+      <c r="BS2" s="3" t="inlineStr">
+        <is>
           <t>BAN DDS LLC</t>
         </is>
       </c>
-      <c r="BS2" s="3" t="inlineStr">
+      <c r="BT2" s="3" t="inlineStr">
         <is>
           <t>225 MAIN STREET</t>
         </is>
       </c>
-      <c r="BT2"/>
-      <c r="BU2" s="3" t="inlineStr">
+      <c r="BU2"/>
+      <c r="BV2" s="3" t="inlineStr">
         <is>
           <t>CENTERVILLE</t>
         </is>
       </c>
-      <c r="BV2" s="3" t="inlineStr">
+      <c r="BW2" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="BW2" s="3" t="inlineStr">
+      <c r="BX2" s="3" t="inlineStr">
         <is>
           <t>17111</t>
         </is>
       </c>
-      <c r="BX2"/>
       <c r="BY2" s="3" t="inlineStr">
         <is>
           <t>PAYEE_IDENTIFICATION_NUMBER</t>
@@ -1801,7 +2574,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906af3</t>
+          <t>6a68fd2aaa71f5c1ede91a9b</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2065,7 +2838,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906af3</t>
+          <t>6a68fd2aaa71f5c1ede91a9b</t>
         </is>
       </c>
       <c r="B4"/>
@@ -2329,7 +3102,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906af3</t>
+          <t>6a68fd2aaa71f5c1ede91a9b</t>
         </is>
       </c>
       <c r="B5"/>
@@ -2593,7 +3366,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906af3</t>
+          <t>6a68fd2aaa71f5c1ede91a9b</t>
         </is>
       </c>
       <c r="B6"/>
@@ -2841,7 +3614,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906af3</t>
+          <t>6a68fd2aaa71f5c1ede91a9b</t>
         </is>
       </c>
       <c r="B7"/>
@@ -3135,7 +3908,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e49906af3</t>
+          <t>6a68fd2aaa71f5c1ede91a9b</t>
         </is>
       </c>
       <c r="B8"/>
